--- a/docs/sheet_template.xlsx
+++ b/docs/sheet_template.xlsx
@@ -111,6 +111,35 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00C62828"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFCDD2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <i val="1"/>
+        <color rgb="009E9E9E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00EEEEEE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="002E7D32"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -489,8 +518,8 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -558,12 +587,12 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>크림업로드가격</t>
+          <t>크림현재입찰가</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>포이즌업로드가격</t>
+          <t>포이즌현재입찰가</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -839,6 +868,17 @@
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
+  <conditionalFormatting sqref="O3:P1000">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>LEFT(O3,3)="오류:"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"off"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"정상"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>